--- a/data/plan_justicia/cubos_completos_plan_justicia.xlsx
+++ b/data/plan_justicia/cubos_completos_plan_justicia.xlsx
@@ -4635,7 +4635,7 @@
         <v>11849</v>
       </c>
       <c r="G159">
-        <v>2367</v>
+        <v>2376</v>
       </c>
       <c r="H159">
         <v>2935</v>
@@ -14905,7 +14905,7 @@
         <v>742</v>
       </c>
       <c r="G554">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H554">
         <v>75</v>
@@ -43661,7 +43661,7 @@
         <v>9120</v>
       </c>
       <c r="G1660">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="H1660">
         <v>1966</v>
@@ -49823,7 +49823,7 @@
         <v>5317</v>
       </c>
       <c r="G1897">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="H1897">
         <v>914</v>

--- a/data/plan_justicia/cubos_completos_plan_justicia.xlsx
+++ b/data/plan_justicia/cubos_completos_plan_justicia.xlsx
@@ -2477,10 +2477,10 @@
         <v>5824</v>
       </c>
       <c r="G76">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="H76">
-        <v>473</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2520,10 +2520,10 @@
         <v>46157</v>
       </c>
       <c r="D78">
-        <v>46462</v>
+        <v>47088</v>
       </c>
       <c r="E78">
-        <v>42590</v>
+        <v>43216</v>
       </c>
       <c r="F78">
         <v>3872</v>
@@ -2546,13 +2546,13 @@
         <v>46188</v>
       </c>
       <c r="D79">
-        <v>41020</v>
+        <v>42266</v>
       </c>
       <c r="E79">
-        <v>36663</v>
+        <v>37797</v>
       </c>
       <c r="F79">
-        <v>4357</v>
+        <v>4469</v>
       </c>
       <c r="G79">
         <v>140</v>
@@ -2572,19 +2572,19 @@
         <v>46218</v>
       </c>
       <c r="D80">
-        <v>21608</v>
+        <v>31811</v>
       </c>
       <c r="E80">
-        <v>18677</v>
+        <v>27773</v>
       </c>
       <c r="F80">
-        <v>2931</v>
+        <v>4038</v>
       </c>
       <c r="G80">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H80">
-        <v>127</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -4626,19 +4626,19 @@
         <v>46218</v>
       </c>
       <c r="D159">
-        <v>101648</v>
+        <v>143316</v>
       </c>
       <c r="E159">
-        <v>89799</v>
+        <v>127371</v>
       </c>
       <c r="F159">
-        <v>11849</v>
+        <v>15945</v>
       </c>
       <c r="G159">
-        <v>2376</v>
+        <v>3482</v>
       </c>
       <c r="H159">
-        <v>2935</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -6628,10 +6628,10 @@
         <v>46157</v>
       </c>
       <c r="D236">
-        <v>11741</v>
+        <v>11758</v>
       </c>
       <c r="E236">
-        <v>11145</v>
+        <v>11162</v>
       </c>
       <c r="F236">
         <v>596</v>
@@ -6654,19 +6654,19 @@
         <v>46188</v>
       </c>
       <c r="D237">
-        <v>12866</v>
+        <v>12930</v>
       </c>
       <c r="E237">
-        <v>12309</v>
+        <v>12351</v>
       </c>
       <c r="F237">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="G237">
         <v>166</v>
       </c>
       <c r="H237">
-        <v>260</v>
+        <v>291</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6680,19 +6680,19 @@
         <v>46218</v>
       </c>
       <c r="D238">
-        <v>6507</v>
+        <v>10129</v>
       </c>
       <c r="E238">
-        <v>5954</v>
+        <v>9561</v>
       </c>
       <c r="F238">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="G238">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H238">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -8682,10 +8682,10 @@
         <v>46157</v>
       </c>
       <c r="D315">
-        <v>1424</v>
+        <v>1441</v>
       </c>
       <c r="E315">
-        <v>1424</v>
+        <v>1441</v>
       </c>
       <c r="F315">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>46188</v>
       </c>
       <c r="D316">
-        <v>522</v>
+        <v>1110</v>
       </c>
       <c r="E316">
-        <v>522</v>
+        <v>1110</v>
       </c>
       <c r="F316">
         <v>0</v>
@@ -8734,10 +8734,10 @@
         <v>46218</v>
       </c>
       <c r="D317">
-        <v>215</v>
+        <v>369</v>
       </c>
       <c r="E317">
-        <v>215</v>
+        <v>369</v>
       </c>
       <c r="F317">
         <v>0</v>
@@ -10762,10 +10762,10 @@
         <v>46188</v>
       </c>
       <c r="D395">
-        <v>2222</v>
+        <v>2106</v>
       </c>
       <c r="E395">
-        <v>2222</v>
+        <v>2106</v>
       </c>
       <c r="F395">
         <v>0</v>
@@ -10788,10 +10788,10 @@
         <v>46218</v>
       </c>
       <c r="D396">
-        <v>814</v>
+        <v>1262</v>
       </c>
       <c r="E396">
-        <v>814</v>
+        <v>1262</v>
       </c>
       <c r="F396">
         <v>0</v>
@@ -12816,10 +12816,10 @@
         <v>46188</v>
       </c>
       <c r="D474">
-        <v>2803</v>
+        <v>3497</v>
       </c>
       <c r="E474">
-        <v>2468</v>
+        <v>3162</v>
       </c>
       <c r="F474">
         <v>335</v>
@@ -12842,13 +12842,13 @@
         <v>46218</v>
       </c>
       <c r="D475">
-        <v>1352</v>
+        <v>2070</v>
       </c>
       <c r="E475">
-        <v>1141</v>
+        <v>1812</v>
       </c>
       <c r="F475">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="G475">
         <v>0</v>
@@ -14844,13 +14844,13 @@
         <v>46157</v>
       </c>
       <c r="D552">
-        <v>11838</v>
+        <v>12174</v>
       </c>
       <c r="E552">
-        <v>10636</v>
+        <v>10964</v>
       </c>
       <c r="F552">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="G552">
         <v>252</v>
@@ -14870,19 +14870,19 @@
         <v>46188</v>
       </c>
       <c r="D553">
-        <v>10478</v>
+        <v>10743</v>
       </c>
       <c r="E553">
-        <v>9122</v>
+        <v>9349</v>
       </c>
       <c r="F553">
-        <v>1356</v>
+        <v>1394</v>
       </c>
       <c r="G553">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H553">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="554" spans="1:8">
@@ -14896,19 +14896,19 @@
         <v>46218</v>
       </c>
       <c r="D554">
-        <v>5076</v>
+        <v>7449</v>
       </c>
       <c r="E554">
-        <v>4334</v>
+        <v>6473</v>
       </c>
       <c r="F554">
-        <v>742</v>
+        <v>976</v>
       </c>
       <c r="G554">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H554">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -16924,10 +16924,10 @@
         <v>46188</v>
       </c>
       <c r="D632">
-        <v>7543</v>
+        <v>7963</v>
       </c>
       <c r="E632">
-        <v>7301</v>
+        <v>7721</v>
       </c>
       <c r="F632">
         <v>242</v>
@@ -16950,19 +16950,19 @@
         <v>46218</v>
       </c>
       <c r="D633">
-        <v>2801</v>
+        <v>4173</v>
       </c>
       <c r="E633">
-        <v>2479</v>
+        <v>3773</v>
       </c>
       <c r="F633">
-        <v>322</v>
+        <v>400</v>
       </c>
       <c r="G633">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H633">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -18952,13 +18952,13 @@
         <v>46157</v>
       </c>
       <c r="D710">
-        <v>48772</v>
+        <v>49975</v>
       </c>
       <c r="E710">
-        <v>42846</v>
+        <v>44016</v>
       </c>
       <c r="F710">
-        <v>5926</v>
+        <v>5959</v>
       </c>
       <c r="G710">
         <v>768</v>
@@ -18978,19 +18978,19 @@
         <v>46188</v>
       </c>
       <c r="D711">
-        <v>40866</v>
+        <v>43057</v>
       </c>
       <c r="E711">
-        <v>35739</v>
+        <v>37483</v>
       </c>
       <c r="F711">
-        <v>5127</v>
+        <v>5574</v>
       </c>
       <c r="G711">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="H711">
-        <v>667</v>
+        <v>685</v>
       </c>
     </row>
     <row r="712" spans="1:8">
@@ -19004,19 +19004,19 @@
         <v>46218</v>
       </c>
       <c r="D712">
-        <v>21673</v>
+        <v>32155</v>
       </c>
       <c r="E712">
-        <v>18590</v>
+        <v>27891</v>
       </c>
       <c r="F712">
-        <v>3083</v>
+        <v>4264</v>
       </c>
       <c r="G712">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="H712">
-        <v>275</v>
+        <v>338</v>
       </c>
     </row>
     <row r="713" spans="1:8">
@@ -21006,10 +21006,10 @@
         <v>46157</v>
       </c>
       <c r="D789">
-        <v>838</v>
+        <v>946</v>
       </c>
       <c r="E789">
-        <v>838</v>
+        <v>946</v>
       </c>
       <c r="F789">
         <v>0</v>
@@ -21032,10 +21032,10 @@
         <v>46188</v>
       </c>
       <c r="D790">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E790">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F790">
         <v>0</v>
@@ -21058,10 +21058,10 @@
         <v>46218</v>
       </c>
       <c r="D791">
-        <v>266</v>
+        <v>369</v>
       </c>
       <c r="E791">
-        <v>266</v>
+        <v>369</v>
       </c>
       <c r="F791">
         <v>0</v>
@@ -21070,7 +21070,7 @@
         <v>0</v>
       </c>
       <c r="H791">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="792" spans="1:8">
@@ -23086,10 +23086,10 @@
         <v>46188</v>
       </c>
       <c r="D869">
-        <v>2567</v>
+        <v>2430</v>
       </c>
       <c r="E869">
-        <v>2567</v>
+        <v>2430</v>
       </c>
       <c r="F869">
         <v>0</v>
@@ -23112,19 +23112,19 @@
         <v>46218</v>
       </c>
       <c r="D870">
-        <v>1140</v>
+        <v>1727</v>
       </c>
       <c r="E870">
-        <v>1140</v>
+        <v>1727</v>
       </c>
       <c r="F870">
         <v>0</v>
       </c>
       <c r="G870">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H870">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="871" spans="1:8">
@@ -25071,7 +25071,7 @@
         <v>3440</v>
       </c>
       <c r="G945">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H945">
         <v>941</v>
@@ -25114,16 +25114,16 @@
         <v>46157</v>
       </c>
       <c r="D947">
-        <v>23334</v>
+        <v>23598</v>
       </c>
       <c r="E947">
-        <v>20520</v>
+        <v>20784</v>
       </c>
       <c r="F947">
         <v>2814</v>
       </c>
       <c r="G947">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H947">
         <v>929</v>
@@ -25140,13 +25140,13 @@
         <v>46188</v>
       </c>
       <c r="D948">
-        <v>23528</v>
+        <v>24423</v>
       </c>
       <c r="E948">
-        <v>20530</v>
+        <v>21351</v>
       </c>
       <c r="F948">
-        <v>2998</v>
+        <v>3072</v>
       </c>
       <c r="G948">
         <v>705</v>
@@ -25166,19 +25166,19 @@
         <v>46218</v>
       </c>
       <c r="D949">
-        <v>12137</v>
+        <v>17095</v>
       </c>
       <c r="E949">
-        <v>11009</v>
+        <v>15362</v>
       </c>
       <c r="F949">
-        <v>1128</v>
+        <v>1733</v>
       </c>
       <c r="G949">
-        <v>393</v>
+        <v>545</v>
       </c>
       <c r="H949">
-        <v>545</v>
+        <v>759</v>
       </c>
     </row>
     <row r="950" spans="1:8">
@@ -27151,7 +27151,7 @@
         <v>8643</v>
       </c>
       <c r="G1025">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1025">
         <v>1847</v>
@@ -27177,7 +27177,7 @@
         <v>8110</v>
       </c>
       <c r="G1026">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1026">
         <v>1385</v>
@@ -27194,19 +27194,19 @@
         <v>46188</v>
       </c>
       <c r="D1027">
-        <v>58537</v>
+        <v>58546</v>
       </c>
       <c r="E1027">
-        <v>48855</v>
+        <v>48863</v>
       </c>
       <c r="F1027">
-        <v>9682</v>
+        <v>9683</v>
       </c>
       <c r="G1027">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="H1027">
-        <v>526</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1028" spans="1:8">
@@ -27220,19 +27220,19 @@
         <v>46218</v>
       </c>
       <c r="D1028">
-        <v>28370</v>
+        <v>33031</v>
       </c>
       <c r="E1028">
-        <v>23265</v>
+        <v>25149</v>
       </c>
       <c r="F1028">
-        <v>5105</v>
+        <v>7882</v>
       </c>
       <c r="G1028">
-        <v>213</v>
+        <v>390</v>
       </c>
       <c r="H1028">
-        <v>356</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1029" spans="1:8">
@@ -29222,10 +29222,10 @@
         <v>46157</v>
       </c>
       <c r="D1105">
-        <v>41235</v>
+        <v>41686</v>
       </c>
       <c r="E1105">
-        <v>38315</v>
+        <v>38766</v>
       </c>
       <c r="F1105">
         <v>2920</v>
@@ -29248,13 +29248,13 @@
         <v>46188</v>
       </c>
       <c r="D1106">
-        <v>37353</v>
+        <v>38099</v>
       </c>
       <c r="E1106">
-        <v>35071</v>
+        <v>35705</v>
       </c>
       <c r="F1106">
-        <v>2282</v>
+        <v>2394</v>
       </c>
       <c r="G1106">
         <v>308</v>
@@ -29274,19 +29274,19 @@
         <v>46218</v>
       </c>
       <c r="D1107">
-        <v>17641</v>
+        <v>25808</v>
       </c>
       <c r="E1107">
-        <v>16385</v>
+        <v>23893</v>
       </c>
       <c r="F1107">
-        <v>1256</v>
+        <v>1915</v>
       </c>
       <c r="G1107">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="H1107">
-        <v>162</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1108" spans="1:8">
@@ -31262,7 +31262,7 @@
         <v>485</v>
       </c>
       <c r="H1183">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1184" spans="1:8">
@@ -31276,13 +31276,13 @@
         <v>46157</v>
       </c>
       <c r="D1184">
-        <v>62682</v>
+        <v>63380</v>
       </c>
       <c r="E1184">
-        <v>59052</v>
+        <v>59733</v>
       </c>
       <c r="F1184">
-        <v>3630</v>
+        <v>3647</v>
       </c>
       <c r="G1184">
         <v>492</v>
@@ -31302,19 +31302,19 @@
         <v>46188</v>
       </c>
       <c r="D1185">
-        <v>62536</v>
+        <v>63341</v>
       </c>
       <c r="E1185">
-        <v>58449</v>
+        <v>59213</v>
       </c>
       <c r="F1185">
-        <v>4087</v>
+        <v>4128</v>
       </c>
       <c r="G1185">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="H1185">
-        <v>1311</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="1186" spans="1:8">
@@ -31328,19 +31328,19 @@
         <v>46218</v>
       </c>
       <c r="D1186">
-        <v>29399</v>
+        <v>44441</v>
       </c>
       <c r="E1186">
-        <v>27154</v>
+        <v>41183</v>
       </c>
       <c r="F1186">
-        <v>2245</v>
+        <v>3258</v>
       </c>
       <c r="G1186">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="H1186">
-        <v>574</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1187" spans="1:8">
@@ -33356,10 +33356,10 @@
         <v>46188</v>
       </c>
       <c r="D1264">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="E1264">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="F1264">
         <v>256</v>
@@ -33382,13 +33382,13 @@
         <v>46218</v>
       </c>
       <c r="D1265">
-        <v>2188</v>
+        <v>2995</v>
       </c>
       <c r="E1265">
-        <v>2001</v>
+        <v>2754</v>
       </c>
       <c r="F1265">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="G1265">
         <v>0</v>
@@ -35436,19 +35436,19 @@
         <v>46218</v>
       </c>
       <c r="D1344">
-        <v>26046</v>
+        <v>38959</v>
       </c>
       <c r="E1344">
-        <v>24605</v>
+        <v>37142</v>
       </c>
       <c r="F1344">
-        <v>1441</v>
+        <v>1817</v>
       </c>
       <c r="G1344">
-        <v>192</v>
+        <v>284</v>
       </c>
       <c r="H1344">
-        <v>223</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1345" spans="1:8">
@@ -37438,10 +37438,10 @@
         <v>46157</v>
       </c>
       <c r="D1421">
-        <v>7862</v>
+        <v>7875</v>
       </c>
       <c r="E1421">
-        <v>7841</v>
+        <v>7854</v>
       </c>
       <c r="F1421">
         <v>21</v>
@@ -37464,10 +37464,10 @@
         <v>46188</v>
       </c>
       <c r="D1422">
-        <v>4135</v>
+        <v>4174</v>
       </c>
       <c r="E1422">
-        <v>4099</v>
+        <v>4138</v>
       </c>
       <c r="F1422">
         <v>36</v>
@@ -37490,19 +37490,19 @@
         <v>46218</v>
       </c>
       <c r="D1423">
-        <v>1586</v>
+        <v>2768</v>
       </c>
       <c r="E1423">
-        <v>1577</v>
+        <v>2756</v>
       </c>
       <c r="F1423">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G1423">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1423">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1424" spans="1:8">
@@ -39475,10 +39475,10 @@
         <v>407</v>
       </c>
       <c r="G1499">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H1499">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1500" spans="1:8">
@@ -39492,10 +39492,10 @@
         <v>46157</v>
       </c>
       <c r="D1500">
-        <v>4999</v>
+        <v>5019</v>
       </c>
       <c r="E1500">
-        <v>4537</v>
+        <v>4557</v>
       </c>
       <c r="F1500">
         <v>462</v>
@@ -39518,10 +39518,10 @@
         <v>46188</v>
       </c>
       <c r="D1501">
-        <v>4820</v>
+        <v>4877</v>
       </c>
       <c r="E1501">
-        <v>4339</v>
+        <v>4396</v>
       </c>
       <c r="F1501">
         <v>481</v>
@@ -39544,19 +39544,19 @@
         <v>46218</v>
       </c>
       <c r="D1502">
-        <v>2698</v>
+        <v>3698</v>
       </c>
       <c r="E1502">
-        <v>2409</v>
+        <v>3325</v>
       </c>
       <c r="F1502">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="G1502">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H1502">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1503" spans="1:8">
@@ -41572,13 +41572,13 @@
         <v>46188</v>
       </c>
       <c r="D1580">
-        <v>3266</v>
+        <v>3386</v>
       </c>
       <c r="E1580">
-        <v>3067</v>
+        <v>3186</v>
       </c>
       <c r="F1580">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G1580">
         <v>50</v>
@@ -41598,13 +41598,13 @@
         <v>46218</v>
       </c>
       <c r="D1581">
-        <v>1887</v>
+        <v>2728</v>
       </c>
       <c r="E1581">
-        <v>1785</v>
+        <v>2578</v>
       </c>
       <c r="F1581">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="G1581">
         <v>0</v>
@@ -43560,7 +43560,7 @@
         <v>2066</v>
       </c>
       <c r="H1656">
-        <v>3967</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="1657" spans="1:8">
@@ -43583,7 +43583,7 @@
         <v>17279</v>
       </c>
       <c r="G1657">
-        <v>1761</v>
+        <v>1770</v>
       </c>
       <c r="H1657">
         <v>3576</v>
@@ -43600,13 +43600,13 @@
         <v>46157</v>
       </c>
       <c r="D1658">
-        <v>110238</v>
+        <v>110428</v>
       </c>
       <c r="E1658">
-        <v>95202</v>
+        <v>95207</v>
       </c>
       <c r="F1658">
-        <v>15036</v>
+        <v>15221</v>
       </c>
       <c r="G1658">
         <v>1963</v>
@@ -43626,19 +43626,19 @@
         <v>46188</v>
       </c>
       <c r="D1659">
-        <v>114312</v>
+        <v>114907</v>
       </c>
       <c r="E1659">
-        <v>99857</v>
+        <v>100450</v>
       </c>
       <c r="F1659">
-        <v>14455</v>
+        <v>14457</v>
       </c>
       <c r="G1659">
-        <v>1509</v>
+        <v>1594</v>
       </c>
       <c r="H1659">
-        <v>3378</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="1660" spans="1:8">
@@ -43652,19 +43652,19 @@
         <v>46218</v>
       </c>
       <c r="D1660">
-        <v>76227</v>
+        <v>100854</v>
       </c>
       <c r="E1660">
-        <v>67107</v>
+        <v>88880</v>
       </c>
       <c r="F1660">
-        <v>9120</v>
+        <v>11974</v>
       </c>
       <c r="G1660">
-        <v>815</v>
+        <v>1225</v>
       </c>
       <c r="H1660">
-        <v>1966</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="1661" spans="1:8">
@@ -45706,13 +45706,13 @@
         <v>46218</v>
       </c>
       <c r="D1739">
-        <v>2182</v>
+        <v>3137</v>
       </c>
       <c r="E1739">
-        <v>1008</v>
+        <v>1479</v>
       </c>
       <c r="F1739">
-        <v>1174</v>
+        <v>1658</v>
       </c>
       <c r="G1739">
         <v>2</v>
@@ -47708,10 +47708,10 @@
         <v>46157</v>
       </c>
       <c r="D1816">
-        <v>31057</v>
+        <v>31406</v>
       </c>
       <c r="E1816">
-        <v>28528</v>
+        <v>28877</v>
       </c>
       <c r="F1816">
         <v>2529</v>
@@ -47734,19 +47734,19 @@
         <v>46188</v>
       </c>
       <c r="D1817">
-        <v>30721</v>
+        <v>31176</v>
       </c>
       <c r="E1817">
-        <v>27475</v>
+        <v>27930</v>
       </c>
       <c r="F1817">
         <v>3246</v>
       </c>
       <c r="G1817">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H1817">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1818" spans="1:8">
@@ -47760,19 +47760,19 @@
         <v>46218</v>
       </c>
       <c r="D1818">
-        <v>15979</v>
+        <v>23376</v>
       </c>
       <c r="E1818">
-        <v>14870</v>
+        <v>21866</v>
       </c>
       <c r="F1818">
-        <v>1109</v>
+        <v>1510</v>
       </c>
       <c r="G1818">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="H1818">
-        <v>205</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1819" spans="1:8">
@@ -49745,10 +49745,10 @@
         <v>7360</v>
       </c>
       <c r="G1894">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="H1894">
-        <v>1884</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1895" spans="1:8">
@@ -49762,19 +49762,19 @@
         <v>46157</v>
       </c>
       <c r="D1895">
-        <v>35734</v>
+        <v>35930</v>
       </c>
       <c r="E1895">
-        <v>27867</v>
+        <v>28060</v>
       </c>
       <c r="F1895">
-        <v>7867</v>
+        <v>7870</v>
       </c>
       <c r="G1895">
         <v>1251</v>
       </c>
       <c r="H1895">
-        <v>1750</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1896" spans="1:8">
@@ -49788,19 +49788,19 @@
         <v>46188</v>
       </c>
       <c r="D1896">
-        <v>37155</v>
+        <v>37459</v>
       </c>
       <c r="E1896">
-        <v>28409</v>
+        <v>28709</v>
       </c>
       <c r="F1896">
-        <v>8746</v>
+        <v>8750</v>
       </c>
       <c r="G1896">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="H1896">
-        <v>1498</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1897" spans="1:8">
@@ -49814,19 +49814,19 @@
         <v>46218</v>
       </c>
       <c r="D1897">
-        <v>21189</v>
+        <v>29576</v>
       </c>
       <c r="E1897">
-        <v>15872</v>
+        <v>22322</v>
       </c>
       <c r="F1897">
-        <v>5317</v>
+        <v>7254</v>
       </c>
       <c r="G1897">
-        <v>750</v>
+        <v>996</v>
       </c>
       <c r="H1897">
-        <v>914</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1898" spans="1:8">
@@ -51790,10 +51790,10 @@
         <v>46127</v>
       </c>
       <c r="D1973">
-        <v>86674</v>
+        <v>86673</v>
       </c>
       <c r="E1973">
-        <v>80685</v>
+        <v>80684</v>
       </c>
       <c r="F1973">
         <v>5989</v>
@@ -51816,19 +51816,19 @@
         <v>46157</v>
       </c>
       <c r="D1974">
-        <v>89110</v>
+        <v>89151</v>
       </c>
       <c r="E1974">
-        <v>82803</v>
+        <v>82844</v>
       </c>
       <c r="F1974">
         <v>6307</v>
       </c>
       <c r="G1974">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1974">
-        <v>1387</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="1975" spans="1:8">
@@ -51842,10 +51842,10 @@
         <v>46188</v>
       </c>
       <c r="D1975">
-        <v>85478</v>
+        <v>85525</v>
       </c>
       <c r="E1975">
-        <v>79639</v>
+        <v>79686</v>
       </c>
       <c r="F1975">
         <v>5839</v>
@@ -51868,19 +51868,19 @@
         <v>46218</v>
       </c>
       <c r="D1976">
-        <v>54763</v>
+        <v>72618</v>
       </c>
       <c r="E1976">
-        <v>50081</v>
+        <v>66253</v>
       </c>
       <c r="F1976">
-        <v>4682</v>
+        <v>6365</v>
       </c>
       <c r="G1976">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="H1976">
-        <v>391</v>
+        <v>704</v>
       </c>
     </row>
     <row r="1977" spans="1:8">
@@ -53896,10 +53896,10 @@
         <v>46188</v>
       </c>
       <c r="D2054">
-        <v>37564</v>
+        <v>37575</v>
       </c>
       <c r="E2054">
-        <v>31878</v>
+        <v>31889</v>
       </c>
       <c r="F2054">
         <v>5686</v>
@@ -53922,13 +53922,13 @@
         <v>46218</v>
       </c>
       <c r="D2055">
-        <v>21826</v>
+        <v>30745</v>
       </c>
       <c r="E2055">
-        <v>18244</v>
+        <v>25848</v>
       </c>
       <c r="F2055">
-        <v>3582</v>
+        <v>4897</v>
       </c>
       <c r="G2055">
         <v>59</v>
@@ -55924,13 +55924,13 @@
         <v>46157</v>
       </c>
       <c r="D2132">
-        <v>36079</v>
+        <v>36119</v>
       </c>
       <c r="E2132">
-        <v>21584</v>
+        <v>21618</v>
       </c>
       <c r="F2132">
-        <v>14495</v>
+        <v>14501</v>
       </c>
       <c r="G2132">
         <v>562</v>
@@ -55950,13 +55950,13 @@
         <v>46188</v>
       </c>
       <c r="D2133">
-        <v>39474</v>
+        <v>39935</v>
       </c>
       <c r="E2133">
-        <v>23312</v>
+        <v>23745</v>
       </c>
       <c r="F2133">
-        <v>16162</v>
+        <v>16190</v>
       </c>
       <c r="G2133">
         <v>876</v>
@@ -55976,19 +55976,19 @@
         <v>46218</v>
       </c>
       <c r="D2134">
-        <v>15206</v>
+        <v>20689</v>
       </c>
       <c r="E2134">
-        <v>13568</v>
+        <v>18563</v>
       </c>
       <c r="F2134">
-        <v>1638</v>
+        <v>2126</v>
       </c>
       <c r="G2134">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="H2134">
-        <v>386</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2135" spans="1:8">
@@ -57978,10 +57978,10 @@
         <v>46157</v>
       </c>
       <c r="D2211">
-        <v>35927</v>
+        <v>35969</v>
       </c>
       <c r="E2211">
-        <v>34703</v>
+        <v>34745</v>
       </c>
       <c r="F2211">
         <v>1224</v>
@@ -58004,13 +58004,13 @@
         <v>46188</v>
       </c>
       <c r="D2212">
-        <v>37049</v>
+        <v>37315</v>
       </c>
       <c r="E2212">
-        <v>35792</v>
+        <v>35946</v>
       </c>
       <c r="F2212">
-        <v>1257</v>
+        <v>1369</v>
       </c>
       <c r="G2212">
         <v>178</v>
@@ -58030,19 +58030,19 @@
         <v>46218</v>
       </c>
       <c r="D2213">
-        <v>17725</v>
+        <v>26975</v>
       </c>
       <c r="E2213">
-        <v>17033</v>
+        <v>25914</v>
       </c>
       <c r="F2213">
-        <v>692</v>
+        <v>1061</v>
       </c>
       <c r="G2213">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="H2213">
-        <v>177</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2214" spans="1:8">
@@ -60032,10 +60032,10 @@
         <v>46157</v>
       </c>
       <c r="D2290">
-        <v>2602</v>
+        <v>2726</v>
       </c>
       <c r="E2290">
-        <v>1526</v>
+        <v>1650</v>
       </c>
       <c r="F2290">
         <v>1076</v>
@@ -60058,10 +60058,10 @@
         <v>46188</v>
       </c>
       <c r="D2291">
-        <v>2654</v>
+        <v>2763</v>
       </c>
       <c r="E2291">
-        <v>1570</v>
+        <v>1679</v>
       </c>
       <c r="F2291">
         <v>1084</v>
@@ -60084,19 +60084,19 @@
         <v>46218</v>
       </c>
       <c r="D2292">
-        <v>1762</v>
+        <v>2747</v>
       </c>
       <c r="E2292">
-        <v>823</v>
+        <v>1467</v>
       </c>
       <c r="F2292">
-        <v>939</v>
+        <v>1280</v>
       </c>
       <c r="G2292">
         <v>13</v>
       </c>
       <c r="H2292">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2293" spans="1:8">
@@ -62086,19 +62086,19 @@
         <v>46157</v>
       </c>
       <c r="D2369">
-        <v>27309</v>
+        <v>27354</v>
       </c>
       <c r="E2369">
-        <v>23105</v>
+        <v>23141</v>
       </c>
       <c r="F2369">
-        <v>4204</v>
+        <v>4213</v>
       </c>
       <c r="G2369">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2369">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="2370" spans="1:8">
@@ -62112,19 +62112,19 @@
         <v>46188</v>
       </c>
       <c r="D2370">
-        <v>26837</v>
+        <v>26946</v>
       </c>
       <c r="E2370">
-        <v>23298</v>
+        <v>23357</v>
       </c>
       <c r="F2370">
-        <v>3539</v>
+        <v>3589</v>
       </c>
       <c r="G2370">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H2370">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2371" spans="1:8">
@@ -62138,19 +62138,19 @@
         <v>46218</v>
       </c>
       <c r="D2371">
-        <v>17313</v>
+        <v>24096</v>
       </c>
       <c r="E2371">
-        <v>14642</v>
+        <v>20430</v>
       </c>
       <c r="F2371">
-        <v>2671</v>
+        <v>3666</v>
       </c>
       <c r="G2371">
-        <v>150</v>
+        <v>269</v>
       </c>
       <c r="H2371">
-        <v>257</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2372" spans="1:8">
@@ -64140,10 +64140,10 @@
         <v>46157</v>
       </c>
       <c r="D2448">
-        <v>23162</v>
+        <v>23158</v>
       </c>
       <c r="E2448">
-        <v>21060</v>
+        <v>21056</v>
       </c>
       <c r="F2448">
         <v>2102</v>
@@ -64166,19 +64166,19 @@
         <v>46188</v>
       </c>
       <c r="D2449">
-        <v>23347</v>
+        <v>23336</v>
       </c>
       <c r="E2449">
-        <v>21132</v>
+        <v>21121</v>
       </c>
       <c r="F2449">
         <v>2215</v>
       </c>
       <c r="G2449">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H2449">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2450" spans="1:8">
@@ -64192,19 +64192,19 @@
         <v>46218</v>
       </c>
       <c r="D2450">
-        <v>15193</v>
+        <v>20243</v>
       </c>
       <c r="E2450">
-        <v>13585</v>
+        <v>17992</v>
       </c>
       <c r="F2450">
-        <v>1608</v>
+        <v>2251</v>
       </c>
       <c r="G2450">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="H2450">
-        <v>239</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2451" spans="1:8">
@@ -66194,16 +66194,16 @@
         <v>46157</v>
       </c>
       <c r="D2527">
-        <v>50174</v>
+        <v>50275</v>
       </c>
       <c r="E2527">
-        <v>47724</v>
+        <v>47825</v>
       </c>
       <c r="F2527">
         <v>2450</v>
       </c>
       <c r="G2527">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2527">
         <v>738</v>
@@ -66220,16 +66220,16 @@
         <v>46188</v>
       </c>
       <c r="D2528">
-        <v>56899</v>
+        <v>57143</v>
       </c>
       <c r="E2528">
-        <v>53543</v>
+        <v>53787</v>
       </c>
       <c r="F2528">
         <v>3356</v>
       </c>
       <c r="G2528">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2528">
         <v>694</v>
@@ -66246,19 +66246,19 @@
         <v>46218</v>
       </c>
       <c r="D2529">
-        <v>30337</v>
+        <v>42133</v>
       </c>
       <c r="E2529">
-        <v>28214</v>
+        <v>39376</v>
       </c>
       <c r="F2529">
-        <v>2123</v>
+        <v>2757</v>
       </c>
       <c r="G2529">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="H2529">
-        <v>286</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
